--- a/artfynd/A 12116-2024 artfynd.xlsx
+++ b/artfynd/A 12116-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117577982</v>
+        <v>117577969</v>
       </c>
       <c r="B2" t="n">
         <v>97836</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443124</v>
+        <v>443112</v>
       </c>
       <c r="R2" t="n">
-        <v>6520153</v>
+        <v>6520143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117578002</v>
+        <v>117577963</v>
       </c>
       <c r="B3" t="n">
-        <v>74531</v>
+        <v>100931</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>693</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Färgginst</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Genista tinctoria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hjortemossen Norr, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443214</v>
+        <v>443156</v>
       </c>
       <c r="R3" t="n">
-        <v>6520242</v>
+        <v>6520160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117577963</v>
+        <v>117577982</v>
       </c>
       <c r="B4" t="n">
-        <v>100931</v>
+        <v>97836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,38 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>693</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Färgginst</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Genista tinctoria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hjortemossen Norr, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443156</v>
+        <v>443124</v>
       </c>
       <c r="R4" t="n">
-        <v>6520160</v>
+        <v>6520153</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +978,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117577983</v>
+        <v>117578002</v>
       </c>
       <c r="B5" t="n">
-        <v>104929</v>
+        <v>74531</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443142</v>
+        <v>443214</v>
       </c>
       <c r="R5" t="n">
-        <v>6520187</v>
+        <v>6520242</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117577969</v>
+        <v>117577976</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>95423</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,25 +1120,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443112</v>
+        <v>443015</v>
       </c>
       <c r="R6" t="n">
-        <v>6520143</v>
+        <v>6520072</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117577976</v>
+        <v>117577983</v>
       </c>
       <c r="B7" t="n">
-        <v>95423</v>
+        <v>104929</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443015</v>
+        <v>443142</v>
       </c>
       <c r="R7" t="n">
-        <v>6520072</v>
+        <v>6520187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 12116-2024 artfynd.xlsx
+++ b/artfynd/A 12116-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117577969</v>
+        <v>117577984</v>
       </c>
       <c r="B2" t="n">
-        <v>97836</v>
+        <v>100933</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>693</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Färgginst</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Genista tinctoria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443112</v>
+        <v>443169</v>
       </c>
       <c r="R2" t="n">
-        <v>6520143</v>
+        <v>6520168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117577963</v>
+        <v>117577982</v>
       </c>
       <c r="B3" t="n">
-        <v>100931</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>693</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Färgginst</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Genista tinctoria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hjortemossen Norr, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443156</v>
+        <v>443124</v>
       </c>
       <c r="R3" t="n">
-        <v>6520160</v>
+        <v>6520153</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117577982</v>
+        <v>117577969</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443124</v>
+        <v>443112</v>
       </c>
       <c r="R4" t="n">
-        <v>6520153</v>
+        <v>6520143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,17 +989,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Liselotte Larsson , Ewa Larsson, Ada  Arenander</t>
+          <t>Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Liselotte Larsson , Ewa Larsson, Ada  Arenander, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117578002</v>
+        <v>117577976</v>
       </c>
       <c r="B5" t="n">
-        <v>74531</v>
+        <v>95425</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443214</v>
+        <v>443015</v>
       </c>
       <c r="R5" t="n">
-        <v>6520242</v>
+        <v>6520072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117577976</v>
+        <v>117577963</v>
       </c>
       <c r="B6" t="n">
-        <v>95423</v>
+        <v>100933</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,38 +1115,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>693</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Färgginst</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Genista tinctoria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hjortemossen Norr, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443015</v>
+        <v>443156</v>
       </c>
       <c r="R6" t="n">
-        <v>6520072</v>
+        <v>6520160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,6 +1191,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>117577983</v>
       </c>
       <c r="B7" t="n">
-        <v>104929</v>
+        <v>104931</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117577984</v>
+        <v>117578002</v>
       </c>
       <c r="B8" t="n">
-        <v>100931</v>
+        <v>74533</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,25 +1334,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>693</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Färgginst</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Genista tinctoria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443169</v>
+        <v>443214</v>
       </c>
       <c r="R8" t="n">
-        <v>6520168</v>
+        <v>6520242</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
